--- a/public/ppni/template2.xlsx
+++ b/public/ppni/template2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/var/rfkbuyani/public/ppni/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF85A25-5C79-E54B-B9FA-5E915ADB2628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DAA564-1091-EF4B-B4F3-612420256C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{A1EBDA47-3DD4-B04C-AEF8-2564DE43E950}"/>
   </bookViews>
@@ -81,14 +81,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -109,18 +108,18 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>16344</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>244944</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -149,7 +148,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="38100"/>
+          <a:off x="1638300" y="76200"/>
           <a:ext cx="6353644" cy="1409700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -157,6 +156,67 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1193800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B37472CC-8BCD-4FE8-F6F6-EC0FA11FF092}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1765300" y="1346200"/>
+          <a:ext cx="6134100" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -479,23 +539,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF14B64A-AAFD-B54E-95A5-824085CAE403}">
-  <dimension ref="A9:C9"/>
+  <dimension ref="A8:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
     <col min="2" max="2" width="57.5" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:3" ht="22" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="8" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:6" ht="22" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
